--- a/trabalho V.P adr/cronograma.xlsx
+++ b/trabalho V.P adr/cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\essjlab2d\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93B6BF40-EE28-4A37-821C-BB6A9A78E83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC1D23D-9FB8-4C92-B409-931DBFEDA634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{17A29B96-9943-4CAC-9BF0-E7512B29AB12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{809EBFD2-93B6-4EC9-A447-68E34BE3FB15}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,27 +37,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>CRONOGRAMA SITE ADRIANA</t>
-  </si>
-  <si>
-    <t>Alunos</t>
-  </si>
-  <si>
-    <t>Entregas</t>
-  </si>
-  <si>
-    <t>Commits</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+  <si>
+    <t>tarefa</t>
+  </si>
+  <si>
+    <t>responsável</t>
+  </si>
+  <si>
+    <t>cronograma</t>
   </si>
   <si>
     <t>Piettro</t>
   </si>
   <si>
+    <t>Página inicial</t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>Divisão de páginas</t>
+  </si>
+  <si>
     <t>João</t>
   </si>
   <si>
+    <t>estilização</t>
+  </si>
+  <si>
+    <t>Divisão de conteúdo</t>
+  </si>
+  <si>
     <t>Danilo</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>concluido</t>
+  </si>
+  <si>
+    <t>em andamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prazo </t>
+  </si>
+  <si>
+    <t>entrega do trabalho Adriana</t>
+  </si>
+  <si>
+    <t>Alunos: Piettro Diniz ; João Batista; Danilo Trevisan</t>
   </si>
 </sst>
 </file>
@@ -73,8 +103,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -82,30 +113,18 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -118,16 +137,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -135,21 +154,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -458,73 +504,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF7A0A1-4448-4EA4-A62B-2B9AE44D200A}">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276AE2E4-0F86-4A0A-B60E-DDA57793F414}">
+  <dimension ref="B1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+    <row r="1" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46135</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46135</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46135</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46135</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5">
+        <v>46135</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4:D8">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"em andamento"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"concluido"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>